--- a/artfynd/A 36903-2026 artfynd.xlsx
+++ b/artfynd/A 36903-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136943555</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136943576</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136943670</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136943800</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136943881</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136944027</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136944083</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136943613</v>
       </c>
       <c r="B9" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136943636</v>
       </c>
       <c r="B10" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136943690</v>
       </c>
       <c r="B11" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136943780</v>
       </c>
       <c r="B12" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136943868</v>
       </c>
       <c r="B13" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136943911</v>
       </c>
       <c r="B14" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136943943</v>
       </c>
       <c r="B15" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136943993</v>
       </c>
       <c r="B16" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>136944011</v>
       </c>
       <c r="B17" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136944057</v>
       </c>
       <c r="B18" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136944033</v>
       </c>
       <c r="B19" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>136943618</v>
       </c>
       <c r="B20" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 36903-2026 artfynd.xlsx
+++ b/artfynd/A 36903-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136943555</v>
       </c>
       <c r="B2" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136943576</v>
       </c>
       <c r="B3" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136943670</v>
       </c>
       <c r="B4" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136943800</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136943881</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136944027</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136944083</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136943613</v>
       </c>
       <c r="B9" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136943636</v>
       </c>
       <c r="B10" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136943690</v>
       </c>
       <c r="B11" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136943780</v>
       </c>
       <c r="B12" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136943868</v>
       </c>
       <c r="B13" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136943911</v>
       </c>
       <c r="B14" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136943943</v>
       </c>
       <c r="B15" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136943993</v>
       </c>
       <c r="B16" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>136944011</v>
       </c>
       <c r="B17" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136944057</v>
       </c>
       <c r="B18" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136944033</v>
       </c>
       <c r="B19" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>136943618</v>
       </c>
       <c r="B20" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 36903-2026 artfynd.xlsx
+++ b/artfynd/A 36903-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136943555</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136943576</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136943670</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136943800</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136943881</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136944027</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136944083</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136943613</v>
       </c>
       <c r="B9" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136943636</v>
       </c>
       <c r="B10" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136943690</v>
       </c>
       <c r="B11" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136943780</v>
       </c>
       <c r="B12" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136943868</v>
       </c>
       <c r="B13" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136943911</v>
       </c>
       <c r="B14" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136943943</v>
       </c>
       <c r="B15" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136943993</v>
       </c>
       <c r="B16" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>136944011</v>
       </c>
       <c r="B17" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136944057</v>
       </c>
       <c r="B18" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136944033</v>
       </c>
       <c r="B19" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>136943618</v>
       </c>
       <c r="B20" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 36903-2026 artfynd.xlsx
+++ b/artfynd/A 36903-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136943555</v>
       </c>
       <c r="B2" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136943576</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136943670</v>
       </c>
       <c r="B4" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136943800</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136943881</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136944027</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136944083</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136943613</v>
       </c>
       <c r="B9" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136943636</v>
       </c>
       <c r="B10" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136943690</v>
       </c>
       <c r="B11" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136943780</v>
       </c>
       <c r="B12" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136943868</v>
       </c>
       <c r="B13" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136943911</v>
       </c>
       <c r="B14" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136943943</v>
       </c>
       <c r="B15" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136943993</v>
       </c>
       <c r="B16" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>136944011</v>
       </c>
       <c r="B17" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136944057</v>
       </c>
       <c r="B18" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136944033</v>
       </c>
       <c r="B19" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>136943618</v>
       </c>
       <c r="B20" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 36903-2026 artfynd.xlsx
+++ b/artfynd/A 36903-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136943555</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136943576</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136943670</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136943800</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136943881</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136944027</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136944083</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136943613</v>
       </c>
       <c r="B9" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136943636</v>
       </c>
       <c r="B10" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136943690</v>
       </c>
       <c r="B11" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136943780</v>
       </c>
       <c r="B12" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136943868</v>
       </c>
       <c r="B13" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136943911</v>
       </c>
       <c r="B14" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136943943</v>
       </c>
       <c r="B15" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136943993</v>
       </c>
       <c r="B16" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>136944011</v>
       </c>
       <c r="B17" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136944057</v>
       </c>
       <c r="B18" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136944033</v>
       </c>
       <c r="B19" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>136943618</v>
       </c>
       <c r="B20" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 36903-2026 artfynd.xlsx
+++ b/artfynd/A 36903-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136943555</v>
       </c>
       <c r="B2" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136943576</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136943670</v>
       </c>
       <c r="B4" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136943800</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136943881</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136944027</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136944083</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136943613</v>
       </c>
       <c r="B9" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136943636</v>
       </c>
       <c r="B10" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136943690</v>
       </c>
       <c r="B11" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136943780</v>
       </c>
       <c r="B12" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136943868</v>
       </c>
       <c r="B13" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136943911</v>
       </c>
       <c r="B14" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136943943</v>
       </c>
       <c r="B15" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136943993</v>
       </c>
       <c r="B16" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>136944011</v>
       </c>
       <c r="B17" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136944057</v>
       </c>
       <c r="B18" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136944033</v>
       </c>
       <c r="B19" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>136943618</v>
       </c>
       <c r="B20" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136943564</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>136943817</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>136943966</v>
       </c>
       <c r="B23" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36903-2026 artfynd.xlsx
+++ b/artfynd/A 36903-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136943555</v>
       </c>
       <c r="B2" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136943576</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136943670</v>
       </c>
       <c r="B4" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136943800</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136943881</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136944027</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136944083</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136943613</v>
       </c>
       <c r="B9" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136943636</v>
       </c>
       <c r="B10" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136943690</v>
       </c>
       <c r="B11" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136943780</v>
       </c>
       <c r="B12" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136943868</v>
       </c>
       <c r="B13" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136943911</v>
       </c>
       <c r="B14" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136943943</v>
       </c>
       <c r="B15" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136943993</v>
       </c>
       <c r="B16" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>136944011</v>
       </c>
       <c r="B17" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136944057</v>
       </c>
       <c r="B18" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136944033</v>
       </c>
       <c r="B19" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>136943618</v>
       </c>
       <c r="B20" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136943564</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>136943817</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>136943966</v>
       </c>
       <c r="B23" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36903-2026 artfynd.xlsx
+++ b/artfynd/A 36903-2026 artfynd.xlsx
@@ -2826,11 +2826,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2941,11 +2937,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3056,11 +3048,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>

--- a/artfynd/A 36903-2026 artfynd.xlsx
+++ b/artfynd/A 36903-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136943555</v>
       </c>
       <c r="B2" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136943576</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136943670</v>
       </c>
       <c r="B4" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136943800</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136943881</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136944027</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136944083</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136943613</v>
       </c>
       <c r="B9" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136943636</v>
       </c>
       <c r="B10" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136943690</v>
       </c>
       <c r="B11" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136943780</v>
       </c>
       <c r="B12" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136943868</v>
       </c>
       <c r="B13" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136943911</v>
       </c>
       <c r="B14" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136943943</v>
       </c>
       <c r="B15" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136943993</v>
       </c>
       <c r="B16" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>136944011</v>
       </c>
       <c r="B17" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136944057</v>
       </c>
       <c r="B18" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136944033</v>
       </c>
       <c r="B19" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>136943618</v>
       </c>
       <c r="B20" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136943564</v>
       </c>
       <c r="B21" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136943817</v>
       </c>
       <c r="B22" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>136943966</v>
       </c>
       <c r="B23" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36903-2026 artfynd.xlsx
+++ b/artfynd/A 36903-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136943555</v>
       </c>
       <c r="B2" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136943576</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136943670</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136943800</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136943881</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136944027</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136944083</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136943613</v>
       </c>
       <c r="B9" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136943636</v>
       </c>
       <c r="B10" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136943690</v>
       </c>
       <c r="B11" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136943780</v>
       </c>
       <c r="B12" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136943868</v>
       </c>
       <c r="B13" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136943911</v>
       </c>
       <c r="B14" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136943943</v>
       </c>
       <c r="B15" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136943993</v>
       </c>
       <c r="B16" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>136944011</v>
       </c>
       <c r="B17" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136944057</v>
       </c>
       <c r="B18" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136944033</v>
       </c>
       <c r="B19" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>136943618</v>
       </c>
       <c r="B20" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136943564</v>
       </c>
       <c r="B21" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136943817</v>
       </c>
       <c r="B22" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>136943966</v>
       </c>
       <c r="B23" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36903-2026 artfynd.xlsx
+++ b/artfynd/A 36903-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136943555</v>
       </c>
       <c r="B2" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136943576</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136943670</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136943800</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136943881</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136944027</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136944083</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136943613</v>
       </c>
       <c r="B9" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136943636</v>
       </c>
       <c r="B10" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136943690</v>
       </c>
       <c r="B11" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136943780</v>
       </c>
       <c r="B12" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136943868</v>
       </c>
       <c r="B13" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136943911</v>
       </c>
       <c r="B14" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136943943</v>
       </c>
       <c r="B15" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136943993</v>
       </c>
       <c r="B16" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>136944011</v>
       </c>
       <c r="B17" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136944057</v>
       </c>
       <c r="B18" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136944033</v>
       </c>
       <c r="B19" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>136943618</v>
       </c>
       <c r="B20" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136943564</v>
       </c>
       <c r="B21" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136943817</v>
       </c>
       <c r="B22" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>136943966</v>
       </c>
       <c r="B23" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36903-2026 artfynd.xlsx
+++ b/artfynd/A 36903-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136943555</v>
       </c>
       <c r="B2" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136943576</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136943670</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136943800</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136943881</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136944027</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136944083</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136943613</v>
       </c>
       <c r="B9" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136943636</v>
       </c>
       <c r="B10" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136943690</v>
       </c>
       <c r="B11" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136943780</v>
       </c>
       <c r="B12" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136943868</v>
       </c>
       <c r="B13" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136943911</v>
       </c>
       <c r="B14" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136943943</v>
       </c>
       <c r="B15" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136943993</v>
       </c>
       <c r="B16" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>136944011</v>
       </c>
       <c r="B17" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136944057</v>
       </c>
       <c r="B18" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136944033</v>
       </c>
       <c r="B19" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>136943618</v>
       </c>
       <c r="B20" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 36903-2026 artfynd.xlsx
+++ b/artfynd/A 36903-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136943555</v>
       </c>
       <c r="B2" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136943576</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136943670</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136943800</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136943881</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136944027</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136944083</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136943613</v>
       </c>
       <c r="B9" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136943636</v>
       </c>
       <c r="B10" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136943690</v>
       </c>
       <c r="B11" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136943780</v>
       </c>
       <c r="B12" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136943868</v>
       </c>
       <c r="B13" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136943911</v>
       </c>
       <c r="B14" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136943943</v>
       </c>
       <c r="B15" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136943993</v>
       </c>
       <c r="B16" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>136944011</v>
       </c>
       <c r="B17" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136944057</v>
       </c>
       <c r="B18" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136944033</v>
       </c>
       <c r="B19" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>136943618</v>
       </c>
       <c r="B20" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 36903-2026 artfynd.xlsx
+++ b/artfynd/A 36903-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136943555</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136943576</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136943670</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136943800</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136943881</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136944027</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136944083</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136943613</v>
       </c>
       <c r="B9" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136943636</v>
       </c>
       <c r="B10" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136943690</v>
       </c>
       <c r="B11" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136943780</v>
       </c>
       <c r="B12" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136943868</v>
       </c>
       <c r="B13" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136943911</v>
       </c>
       <c r="B14" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136943943</v>
       </c>
       <c r="B15" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136943993</v>
       </c>
       <c r="B16" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>136944011</v>
       </c>
       <c r="B17" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136944057</v>
       </c>
       <c r="B18" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136944033</v>
       </c>
       <c r="B19" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>136943618</v>
       </c>
       <c r="B20" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 36903-2026 artfynd.xlsx
+++ b/artfynd/A 36903-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136943555</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136943576</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136943670</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136943800</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136943881</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136944027</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136944083</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136943613</v>
       </c>
       <c r="B9" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136943636</v>
       </c>
       <c r="B10" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136943690</v>
       </c>
       <c r="B11" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136943780</v>
       </c>
       <c r="B12" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136943868</v>
       </c>
       <c r="B13" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136943911</v>
       </c>
       <c r="B14" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136943943</v>
       </c>
       <c r="B15" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136943993</v>
       </c>
       <c r="B16" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>136944011</v>
       </c>
       <c r="B17" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136944057</v>
       </c>
       <c r="B18" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136944033</v>
       </c>
       <c r="B19" t="n">
-        <v>80655</v>
+        <v>80656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>136943618</v>
       </c>
       <c r="B20" t="n">
-        <v>80661</v>
+        <v>80662</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 36903-2026 artfynd.xlsx
+++ b/artfynd/A 36903-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136943555</v>
       </c>
       <c r="B2" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136943576</v>
       </c>
       <c r="B3" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136943670</v>
       </c>
       <c r="B4" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136943800</v>
       </c>
       <c r="B5" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136943881</v>
       </c>
       <c r="B6" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136944027</v>
       </c>
       <c r="B7" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136944083</v>
       </c>
       <c r="B8" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136943613</v>
       </c>
       <c r="B9" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136943636</v>
       </c>
       <c r="B10" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136943690</v>
       </c>
       <c r="B11" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136943780</v>
       </c>
       <c r="B12" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136943868</v>
       </c>
       <c r="B13" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136943911</v>
       </c>
       <c r="B14" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136943943</v>
       </c>
       <c r="B15" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136943993</v>
       </c>
       <c r="B16" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>136944011</v>
       </c>
       <c r="B17" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136944057</v>
       </c>
       <c r="B18" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136944033</v>
       </c>
       <c r="B19" t="n">
-        <v>80656</v>
+        <v>80659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>136943618</v>
       </c>
       <c r="B20" t="n">
-        <v>80662</v>
+        <v>80665</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136943564</v>
       </c>
       <c r="B21" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136943817</v>
       </c>
       <c r="B22" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>136943966</v>
       </c>
       <c r="B23" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
